--- a/Fase 2/Evidencias Proyecto/Evidencias de documentación/Sprint 2/Ev. Burndown Chart.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de documentación/Sprint 2/Ev. Burndown Chart.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Dia</t>
   </si>
@@ -71,16 +71,13 @@
   </si>
   <si>
     <t>Integración de mapa interactivo</t>
-  </si>
-  <si>
-    <t>HOY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -101,13 +98,8 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -146,8 +138,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6D9EEB"/>
+        <bgColor rgb="FF6D9EEB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6FA8DC"/>
+        <bgColor rgb="FF6FA8DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE69138"/>
+        <bgColor rgb="FFE69138"/>
       </patternFill>
     </fill>
   </fills>
@@ -157,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -194,17 +204,32 @@
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf borderId="0" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -311,11 +336,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="2022744582"/>
-        <c:axId val="1557790823"/>
+        <c:axId val="914886287"/>
+        <c:axId val="846187726"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="2022744582"/>
+        <c:axId val="914886287"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -371,10 +396,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1557790823"/>
+        <c:crossAx val="846187726"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1557790823"/>
+        <c:axId val="846187726"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -451,7 +476,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2022744582"/>
+        <c:crossAx val="914886287"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -1013,7 +1038,7 @@
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="12">
+      <c r="L11" s="13">
         <v>15.0</v>
       </c>
       <c r="M11" s="6" t="s">
@@ -1040,7 +1065,7 @@
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
-      <c r="L12" s="12">
+      <c r="L12" s="13">
         <v>15.0</v>
       </c>
       <c r="M12" s="6" t="s">
@@ -1066,7 +1091,7 @@
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
-      <c r="L13" s="12">
+      <c r="L13" s="14">
         <v>15.0</v>
       </c>
       <c r="M13" s="6" t="s">
@@ -1081,7 +1106,7 @@
         <f t="shared" si="1"/>
         <v>111.4285714</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="15">
         <f>C13-10</f>
         <v>75</v>
       </c>
@@ -1092,7 +1117,7 @@
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
-      <c r="L14" s="12">
+      <c r="L14" s="16">
         <v>15.0</v>
       </c>
       <c r="M14" s="6" t="s">
@@ -1108,7 +1133,7 @@
         <v>104.4642857</v>
       </c>
       <c r="C15" s="3">
-        <f t="shared" ref="C15:C29" si="4">C14-0</f>
+        <f t="shared" ref="C15:C21" si="4">C14-0</f>
         <v>75</v>
       </c>
       <c r="E15" s="2"/>
@@ -1118,7 +1143,7 @@
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
-      <c r="L15" s="14">
+      <c r="L15" s="17">
         <v>10.0</v>
       </c>
       <c r="M15" s="6" t="s">
@@ -1180,9 +1205,7 @@
         <f t="shared" si="4"/>
         <v>75</v>
       </c>
-      <c r="D18" s="15" t="s">
-        <v>20</v>
-      </c>
+      <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -1266,11 +1289,10 @@
         <f t="shared" si="1"/>
         <v>55.71428571</v>
       </c>
-      <c r="C22" s="3">
-        <f t="shared" si="4"/>
-        <v>75</v>
-      </c>
-      <c r="D22" s="2"/>
+      <c r="C22" s="18">
+        <f>C21-45</f>
+        <v>30</v>
+      </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
@@ -1289,8 +1311,8 @@
         <v>48.75</v>
       </c>
       <c r="C23" s="3">
-        <f t="shared" si="4"/>
-        <v>75</v>
+        <f t="shared" ref="C23:C25" si="5">C22-0</f>
+        <v>30</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -1311,8 +1333,8 @@
         <v>41.78571429</v>
       </c>
       <c r="C24" s="3">
-        <f t="shared" si="4"/>
-        <v>75</v>
+        <f t="shared" si="5"/>
+        <v>30</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -1333,10 +1355,9 @@
         <v>34.82142857</v>
       </c>
       <c r="C25" s="3">
-        <f t="shared" si="4"/>
-        <v>75</v>
-      </c>
-      <c r="D25" s="2"/>
+        <f t="shared" si="5"/>
+        <v>30</v>
+      </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -1354,11 +1375,10 @@
         <f t="shared" si="1"/>
         <v>27.85714286</v>
       </c>
-      <c r="C26" s="3">
-        <f t="shared" si="4"/>
-        <v>75</v>
-      </c>
-      <c r="D26" s="2"/>
+      <c r="C26" s="19">
+        <f t="shared" ref="C26:C27" si="6">C25-15</f>
+        <v>15</v>
+      </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -1376,9 +1396,9 @@
         <f t="shared" si="1"/>
         <v>20.89285714</v>
       </c>
-      <c r="C27" s="3">
-        <f t="shared" si="4"/>
-        <v>75</v>
+      <c r="C27" s="20">
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
@@ -1399,8 +1419,8 @@
         <v>13.92857143</v>
       </c>
       <c r="C28" s="3">
-        <f t="shared" si="4"/>
-        <v>75</v>
+        <f t="shared" ref="C28:C29" si="7">C27-0</f>
+        <v>0</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
@@ -1421,8 +1441,8 @@
         <v>6.964285714</v>
       </c>
       <c r="C29" s="3">
-        <f t="shared" si="4"/>
-        <v>75</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
